--- a/Selecionados_Motivacional_Ribaue_2026.xlsx
+++ b/Selecionados_Motivacional_Ribaue_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Processos de Selecao/Processo para beneficiarios/Abrindo_Oportunidades/2026/Mobilizacao/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/Abrindo_Oportunidades/2026/Dash_Abrindo_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_F833A363A5E9B997DDF5DE690BDD84802C57B85D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{910D81C2-D621-43A6-B973-05AA3CFE16A8}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_F833A363A5E9B997DDF5DE690BDD84802C57B85D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC16045-D8FA-4B38-801B-465B84FE8500}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22509" uniqueCount="5487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22699" uniqueCount="5518">
   <si>
     <t>interview__key</t>
   </si>
@@ -16481,6 +16481,99 @@
   </si>
   <si>
     <t>AO_2026_0645</t>
+  </si>
+  <si>
+    <t>CURRAPE</t>
+  </si>
+  <si>
+    <t>50-48-40-68</t>
+  </si>
+  <si>
+    <t>55df4db44d664b88a843c94887c9432a</t>
+  </si>
+  <si>
+    <t>2026-02-12T14:00:49</t>
+  </si>
+  <si>
+    <t>2026-02-12T12:01:03</t>
+  </si>
+  <si>
+    <t>842-467-516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELMA SEBASTIAO </t>
+  </si>
+  <si>
+    <t>92-48-77-80</t>
+  </si>
+  <si>
+    <t>98abd1e8009242ec9a5473bfe2603cba</t>
+  </si>
+  <si>
+    <t>BELACIA AGOSTINHO</t>
+  </si>
+  <si>
+    <t>2026-02-12T14:43:03</t>
+  </si>
+  <si>
+    <t>06-19-93-56</t>
+  </si>
+  <si>
+    <t>6c9f74ade1024c338b038dd03ffec821</t>
+  </si>
+  <si>
+    <t>RIANNE</t>
+  </si>
+  <si>
+    <t>2026-02-12T14:11:13</t>
+  </si>
+  <si>
+    <t>2026-02-12T12:11:13</t>
+  </si>
+  <si>
+    <t>HORTENCIA FLORENCIO</t>
+  </si>
+  <si>
+    <t>66-69-55-74</t>
+  </si>
+  <si>
+    <t>abab4f0759924dcf8f280aa233f43f98</t>
+  </si>
+  <si>
+    <t>2026-02-16T10:42:15</t>
+  </si>
+  <si>
+    <t>090208-19052348534(090348-01/324)</t>
+  </si>
+  <si>
+    <t>MILHO , FEIJAO BOER,  CEBOLA, GERGELIM</t>
+  </si>
+  <si>
+    <t>878-389-750</t>
+  </si>
+  <si>
+    <t>AURORA ALIANTE</t>
+  </si>
+  <si>
+    <t>01-02-64-22</t>
+  </si>
+  <si>
+    <t>c7d1109bb8d8437c9d72e7a1d157d57e</t>
+  </si>
+  <si>
+    <t>2026-02-16T11:33:46</t>
+  </si>
+  <si>
+    <t>090348-04/364</t>
+  </si>
+  <si>
+    <t>DIFICULDADES DE AUDICAO E FALA</t>
+  </si>
+  <si>
+    <t>JULIAO GABRIEL</t>
+  </si>
+  <si>
+    <t>RICARDINA JULIO</t>
   </si>
 </sst>
 </file>
@@ -16567,8 +16660,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E9F7243-0B27-4568-942D-7201B3F0C08F}" name="Table1" displayName="Table1" ref="A1:AX646" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:AX646" xr:uid="{0E9F7243-0B27-4568-942D-7201B3F0C08F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E9F7243-0B27-4568-942D-7201B3F0C08F}" name="Table1" displayName="Table1" ref="A1:AX652" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:AX652" xr:uid="{0E9F7243-0B27-4568-942D-7201B3F0C08F}"/>
   <tableColumns count="50">
     <tableColumn id="1" xr3:uid="{9FC13388-9F59-463F-9535-1E06DD20884E}" name="interview__key"/>
     <tableColumn id="2" xr3:uid="{AB23A961-9E83-4AB5-B367-21C1014FF006}" name="interview__id"/>
@@ -16912,7 +17005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX646"/>
+  <dimension ref="A1:AX652"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.21875" customWidth="1"/>
@@ -17130,7 +17223,7 @@
         <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F2" t="s">
         <v>54</v>
@@ -17264,7 +17357,7 @@
         <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
@@ -17395,7 +17488,7 @@
         <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
@@ -17520,7 +17613,7 @@
         <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F5" t="s">
         <v>54</v>
@@ -17654,7 +17747,7 @@
         <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
@@ -17776,7 +17869,7 @@
         <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
@@ -17907,7 +18000,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F8" t="s">
         <v>54</v>
@@ -18038,7 +18131,7 @@
         <v>53</v>
       </c>
       <c r="E9" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F9" t="s">
         <v>54</v>
@@ -18163,7 +18256,7 @@
         <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F10" t="s">
         <v>54</v>
@@ -18300,7 +18393,7 @@
         <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -18431,7 +18524,7 @@
         <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F12" t="s">
         <v>54</v>
@@ -18559,7 +18652,7 @@
         <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F13" t="s">
         <v>54</v>
@@ -18690,7 +18783,7 @@
         <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F14" t="s">
         <v>54</v>
@@ -18818,7 +18911,7 @@
         <v>53</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F15" t="s">
         <v>54</v>
@@ -18952,7 +19045,7 @@
         <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F16" t="s">
         <v>54</v>
@@ -19080,7 +19173,7 @@
         <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F17" t="s">
         <v>54</v>
@@ -19205,7 +19298,7 @@
         <v>53</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F18" t="s">
         <v>54</v>
@@ -19327,7 +19420,7 @@
         <v>53</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F19" t="s">
         <v>54</v>
@@ -19458,7 +19551,7 @@
         <v>53</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F20" t="s">
         <v>54</v>
@@ -19583,7 +19676,7 @@
         <v>53</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F21" t="s">
         <v>54</v>
@@ -19711,7 +19804,7 @@
         <v>53</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F22" t="s">
         <v>54</v>
@@ -19833,7 +19926,7 @@
         <v>53</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F23" t="s">
         <v>54</v>
@@ -19970,7 +20063,7 @@
         <v>53</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F24" t="s">
         <v>54</v>
@@ -20104,7 +20197,7 @@
         <v>53</v>
       </c>
       <c r="E25" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F25" t="s">
         <v>54</v>
@@ -20235,7 +20328,7 @@
         <v>53</v>
       </c>
       <c r="E26" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F26" t="s">
         <v>54</v>
@@ -20360,7 +20453,7 @@
         <v>53</v>
       </c>
       <c r="E27" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F27" t="s">
         <v>54</v>
@@ -20491,7 +20584,7 @@
         <v>53</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F28" t="s">
         <v>312</v>
@@ -20619,7 +20712,7 @@
         <v>53</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F29" t="s">
         <v>54</v>
@@ -20750,7 +20843,7 @@
         <v>53</v>
       </c>
       <c r="E30" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F30" t="s">
         <v>54</v>
@@ -20881,7 +20974,7 @@
         <v>53</v>
       </c>
       <c r="E31" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F31" t="s">
         <v>54</v>
@@ -21003,7 +21096,7 @@
         <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F32" t="s">
         <v>54</v>
@@ -21125,7 +21218,7 @@
         <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F33" t="s">
         <v>54</v>
@@ -21265,7 +21358,7 @@
         <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F34" t="s">
         <v>54</v>
@@ -21387,7 +21480,7 @@
         <v>53</v>
       </c>
       <c r="E35" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F35" t="s">
         <v>54</v>
@@ -21518,7 +21611,7 @@
         <v>53</v>
       </c>
       <c r="E36" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F36" t="s">
         <v>54</v>
@@ -21640,7 +21733,7 @@
         <v>53</v>
       </c>
       <c r="E37" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F37" t="s">
         <v>54</v>
@@ -21762,7 +21855,7 @@
         <v>53</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F38" t="s">
         <v>54</v>
@@ -21893,7 +21986,7 @@
         <v>53</v>
       </c>
       <c r="E39" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F39" t="s">
         <v>54</v>
@@ -22015,7 +22108,7 @@
         <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F40" t="s">
         <v>54</v>
@@ -22143,7 +22236,7 @@
         <v>53</v>
       </c>
       <c r="E41" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F41" t="s">
         <v>54</v>
@@ -22277,7 +22370,7 @@
         <v>53</v>
       </c>
       <c r="E42" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F42" t="s">
         <v>54</v>
@@ -22405,7 +22498,7 @@
         <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F43" t="s">
         <v>54</v>
@@ -22527,7 +22620,7 @@
         <v>53</v>
       </c>
       <c r="E44" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F44" t="s">
         <v>54</v>
@@ -22649,7 +22742,7 @@
         <v>53</v>
       </c>
       <c r="E45" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F45" t="s">
         <v>54</v>
@@ -22780,7 +22873,7 @@
         <v>53</v>
       </c>
       <c r="E46" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F46" t="s">
         <v>54</v>
@@ -22911,7 +23004,7 @@
         <v>53</v>
       </c>
       <c r="E47" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F47" t="s">
         <v>54</v>
@@ -23042,7 +23135,7 @@
         <v>53</v>
       </c>
       <c r="E48" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F48" t="s">
         <v>54</v>
@@ -23173,7 +23266,7 @@
         <v>53</v>
       </c>
       <c r="E49" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F49" t="s">
         <v>54</v>
@@ -23304,7 +23397,7 @@
         <v>53</v>
       </c>
       <c r="E50" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F50" t="s">
         <v>54</v>
@@ -23429,7 +23522,7 @@
         <v>53</v>
       </c>
       <c r="E51" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F51" t="s">
         <v>54</v>
@@ -23551,7 +23644,7 @@
         <v>53</v>
       </c>
       <c r="E52" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F52" t="s">
         <v>54</v>
@@ -23682,7 +23775,7 @@
         <v>53</v>
       </c>
       <c r="E53" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F53" t="s">
         <v>54</v>
@@ -23813,7 +23906,7 @@
         <v>53</v>
       </c>
       <c r="E54" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F54" t="s">
         <v>54</v>
@@ -23941,7 +24034,7 @@
         <v>53</v>
       </c>
       <c r="E55" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F55" t="s">
         <v>54</v>
@@ -24072,7 +24165,7 @@
         <v>53</v>
       </c>
       <c r="E56" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F56" t="s">
         <v>54</v>
@@ -24203,7 +24296,7 @@
         <v>53</v>
       </c>
       <c r="E57" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F57" t="s">
         <v>54</v>
@@ -24331,7 +24424,7 @@
         <v>53</v>
       </c>
       <c r="E58" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F58" t="s">
         <v>54</v>
@@ -24453,7 +24546,7 @@
         <v>53</v>
       </c>
       <c r="E59" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F59" t="s">
         <v>54</v>
@@ -24575,7 +24668,7 @@
         <v>53</v>
       </c>
       <c r="E60" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F60" t="s">
         <v>54</v>
@@ -24697,7 +24790,7 @@
         <v>53</v>
       </c>
       <c r="E61" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F61" t="s">
         <v>54</v>
@@ -24825,7 +24918,7 @@
         <v>53</v>
       </c>
       <c r="E62" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F62" t="s">
         <v>54</v>
@@ -24953,7 +25046,7 @@
         <v>53</v>
       </c>
       <c r="E63" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F63" t="s">
         <v>54</v>
@@ -25081,7 +25174,7 @@
         <v>53</v>
       </c>
       <c r="E64" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F64" t="s">
         <v>54</v>
@@ -25203,7 +25296,7 @@
         <v>53</v>
       </c>
       <c r="E65" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F65" t="s">
         <v>54</v>
@@ -25331,7 +25424,7 @@
         <v>53</v>
       </c>
       <c r="E66" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F66" t="s">
         <v>54</v>
@@ -25462,7 +25555,7 @@
         <v>53</v>
       </c>
       <c r="E67" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F67" t="s">
         <v>54</v>
@@ -25587,7 +25680,7 @@
         <v>53</v>
       </c>
       <c r="E68" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F68" t="s">
         <v>54</v>
@@ -25718,7 +25811,7 @@
         <v>53</v>
       </c>
       <c r="E69" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F69" t="s">
         <v>54</v>
@@ -25846,7 +25939,7 @@
         <v>53</v>
       </c>
       <c r="E70" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F70" t="s">
         <v>54</v>
@@ -25974,7 +26067,7 @@
         <v>53</v>
       </c>
       <c r="E71" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F71" t="s">
         <v>54</v>
@@ -26102,7 +26195,7 @@
         <v>53</v>
       </c>
       <c r="E72" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F72" t="s">
         <v>54</v>
@@ -26233,7 +26326,7 @@
         <v>53</v>
       </c>
       <c r="E73" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F73" t="s">
         <v>54</v>
@@ -26367,7 +26460,7 @@
         <v>53</v>
       </c>
       <c r="E74" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F74" t="s">
         <v>54</v>
@@ -26489,7 +26582,7 @@
         <v>53</v>
       </c>
       <c r="E75" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F75" t="s">
         <v>54</v>
@@ -26617,7 +26710,7 @@
         <v>53</v>
       </c>
       <c r="E76" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F76" t="s">
         <v>54</v>
@@ -26745,7 +26838,7 @@
         <v>53</v>
       </c>
       <c r="E77" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F77" t="s">
         <v>54</v>
@@ -26876,7 +26969,7 @@
         <v>53</v>
       </c>
       <c r="E78" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F78" t="s">
         <v>54</v>
@@ -27001,7 +27094,7 @@
         <v>53</v>
       </c>
       <c r="E79" t="s">
-        <v>54</v>
+        <v>5487</v>
       </c>
       <c r="F79" t="s">
         <v>54</v>
@@ -101531,6 +101624,729 @@
       </c>
       <c r="AX646" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="647" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A647" t="s">
+        <v>5488</v>
+      </c>
+      <c r="B647" t="s">
+        <v>5489</v>
+      </c>
+      <c r="C647" t="s">
+        <v>52</v>
+      </c>
+      <c r="D647" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E647" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F647" t="s">
+        <v>2252</v>
+      </c>
+      <c r="G647" t="s">
+        <v>110</v>
+      </c>
+      <c r="I647" t="s">
+        <v>56</v>
+      </c>
+      <c r="K647" t="s">
+        <v>5493</v>
+      </c>
+      <c r="L647" t="s">
+        <v>5490</v>
+      </c>
+      <c r="M647">
+        <v>-15.0254013</v>
+      </c>
+      <c r="N647">
+        <v>38.0460207</v>
+      </c>
+      <c r="O647">
+        <v>47641.21484375</v>
+      </c>
+      <c r="Q647" t="s">
+        <v>5491</v>
+      </c>
+      <c r="R647" t="s">
+        <v>65</v>
+      </c>
+      <c r="U647" t="s">
+        <v>61</v>
+      </c>
+      <c r="V647">
+        <v>1996</v>
+      </c>
+      <c r="W647">
+        <v>29</v>
+      </c>
+      <c r="X647" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y647" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z647" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA647" t="s">
+        <v>905</v>
+      </c>
+      <c r="AB647" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC647" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE647" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF647" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG647" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH647" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI647" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM647" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN647" t="s">
+        <v>495</v>
+      </c>
+      <c r="AO647" t="s">
+        <v>5492</v>
+      </c>
+      <c r="AP647" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS647" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT647">
+        <v>0.35504143887899881</v>
+      </c>
+      <c r="AU647">
+        <v>0</v>
+      </c>
+      <c r="AV647" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW647">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="648" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A648" t="s">
+        <v>5494</v>
+      </c>
+      <c r="B648" t="s">
+        <v>5495</v>
+      </c>
+      <c r="C648" t="s">
+        <v>52</v>
+      </c>
+      <c r="D648" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E648" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F648" t="s">
+        <v>2252</v>
+      </c>
+      <c r="G648" t="s">
+        <v>759</v>
+      </c>
+      <c r="I648" t="s">
+        <v>56</v>
+      </c>
+      <c r="K648" t="s">
+        <v>5496</v>
+      </c>
+      <c r="L648" t="s">
+        <v>5497</v>
+      </c>
+      <c r="M648">
+        <v>-14.9607463</v>
+      </c>
+      <c r="N648">
+        <v>38.1488826</v>
+      </c>
+      <c r="O648">
+        <v>2700</v>
+      </c>
+      <c r="Q648" t="s">
+        <v>2281</v>
+      </c>
+      <c r="R648" t="s">
+        <v>65</v>
+      </c>
+      <c r="U648" t="s">
+        <v>61</v>
+      </c>
+      <c r="V648">
+        <v>2003</v>
+      </c>
+      <c r="W648">
+        <v>23</v>
+      </c>
+      <c r="X648" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y648" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z648" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA648" t="s">
+        <v>2137</v>
+      </c>
+      <c r="AB648" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC648" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE648" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF648" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG648" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH648" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI648" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM648" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN648" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO648" t="s">
+        <v>2284</v>
+      </c>
+      <c r="AP648" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS648" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT648">
+        <v>0.91727330205835089</v>
+      </c>
+      <c r="AU648">
+        <v>0</v>
+      </c>
+      <c r="AV648" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW648">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="649" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A649" t="s">
+        <v>5498</v>
+      </c>
+      <c r="B649" t="s">
+        <v>5499</v>
+      </c>
+      <c r="C649" t="s">
+        <v>52</v>
+      </c>
+      <c r="D649" t="s">
+        <v>5500</v>
+      </c>
+      <c r="E649" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F649" t="s">
+        <v>2252</v>
+      </c>
+      <c r="G649" t="s">
+        <v>110</v>
+      </c>
+      <c r="I649" t="s">
+        <v>56</v>
+      </c>
+      <c r="K649" t="s">
+        <v>5503</v>
+      </c>
+      <c r="L649" t="s">
+        <v>5501</v>
+      </c>
+      <c r="M649">
+        <v>-15.0254013</v>
+      </c>
+      <c r="N649">
+        <v>38.0460207</v>
+      </c>
+      <c r="O649">
+        <v>51911.07421875</v>
+      </c>
+      <c r="Q649" t="s">
+        <v>5502</v>
+      </c>
+      <c r="R649" t="s">
+        <v>65</v>
+      </c>
+      <c r="U649" t="s">
+        <v>61</v>
+      </c>
+      <c r="V649">
+        <v>1994</v>
+      </c>
+      <c r="W649">
+        <v>32</v>
+      </c>
+      <c r="X649" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y649" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z649" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA649" t="s">
+        <v>3014</v>
+      </c>
+      <c r="AB649" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC649" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE649" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF649" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG649" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH649" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI649" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM649" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN649" t="s">
+        <v>135</v>
+      </c>
+      <c r="AO649" t="s">
+        <v>2502</v>
+      </c>
+      <c r="AP649" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ649" t="s">
+        <v>135</v>
+      </c>
+      <c r="AR649" t="s">
+        <v>2294</v>
+      </c>
+      <c r="AS649" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT649">
+        <v>0.5140524900118133</v>
+      </c>
+      <c r="AU649">
+        <v>0</v>
+      </c>
+      <c r="AV649" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW649">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="650" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A650" t="s">
+        <v>5504</v>
+      </c>
+      <c r="B650" t="s">
+        <v>5505</v>
+      </c>
+      <c r="C650" t="s">
+        <v>52</v>
+      </c>
+      <c r="D650" t="s">
+        <v>53</v>
+      </c>
+      <c r="E650" t="s">
+        <v>4156</v>
+      </c>
+      <c r="F650" t="s">
+        <v>4156</v>
+      </c>
+      <c r="G650" t="s">
+        <v>55</v>
+      </c>
+      <c r="I650" t="s">
+        <v>56</v>
+      </c>
+      <c r="K650" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L650" t="s">
+        <v>5506</v>
+      </c>
+      <c r="Q650" t="s">
+        <v>57</v>
+      </c>
+      <c r="R650" t="s">
+        <v>56</v>
+      </c>
+      <c r="S650" t="s">
+        <v>59</v>
+      </c>
+      <c r="T650" t="s">
+        <v>5507</v>
+      </c>
+      <c r="U650" t="s">
+        <v>61</v>
+      </c>
+      <c r="V650">
+        <v>2003</v>
+      </c>
+      <c r="W650">
+        <v>23</v>
+      </c>
+      <c r="X650" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y650" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z650" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA650" t="s">
+        <v>5508</v>
+      </c>
+      <c r="AB650" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC650" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD650" t="s">
+        <v>1558</v>
+      </c>
+      <c r="AE650" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF650" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG650" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH650" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI650" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ650" t="s">
+        <v>5509</v>
+      </c>
+      <c r="AK650" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM650" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT650">
+        <v>0.99299353919597044</v>
+      </c>
+      <c r="AU650">
+        <v>0</v>
+      </c>
+      <c r="AV650" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW650">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="651" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A651" t="s">
+        <v>5511</v>
+      </c>
+      <c r="B651" t="s">
+        <v>5512</v>
+      </c>
+      <c r="C651" t="s">
+        <v>52</v>
+      </c>
+      <c r="D651" t="s">
+        <v>53</v>
+      </c>
+      <c r="E651" t="s">
+        <v>4156</v>
+      </c>
+      <c r="F651" t="s">
+        <v>4156</v>
+      </c>
+      <c r="G651" t="s">
+        <v>769</v>
+      </c>
+      <c r="H651" t="s">
+        <v>770</v>
+      </c>
+      <c r="I651" t="s">
+        <v>56</v>
+      </c>
+      <c r="K651" t="s">
+        <v>5516</v>
+      </c>
+      <c r="L651" t="s">
+        <v>5513</v>
+      </c>
+      <c r="M651">
+        <v>-14.944211299999999</v>
+      </c>
+      <c r="N651">
+        <v>38.321587800000003</v>
+      </c>
+      <c r="O651">
+        <v>98.400001525878906</v>
+      </c>
+      <c r="P651">
+        <v>516.89996337890625</v>
+      </c>
+      <c r="Q651" t="s">
+        <v>4239</v>
+      </c>
+      <c r="R651" t="s">
+        <v>56</v>
+      </c>
+      <c r="S651" t="s">
+        <v>59</v>
+      </c>
+      <c r="T651" t="s">
+        <v>5514</v>
+      </c>
+      <c r="U651" t="s">
+        <v>102</v>
+      </c>
+      <c r="V651">
+        <v>2003</v>
+      </c>
+      <c r="W651">
+        <v>23</v>
+      </c>
+      <c r="X651" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y651" t="s">
+        <v>5515</v>
+      </c>
+      <c r="Z651" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA651" t="s">
+        <v>1280</v>
+      </c>
+      <c r="AB651" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC651" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE651" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF651" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG651" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH651" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI651" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ651" t="s">
+        <v>4465</v>
+      </c>
+      <c r="AK651" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM651" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT651">
+        <v>0.76560934389271273</v>
+      </c>
+      <c r="AU651">
+        <v>0</v>
+      </c>
+      <c r="AV651" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW651">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="652" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A652" t="s">
+        <v>4999</v>
+      </c>
+      <c r="B652" t="s">
+        <v>5000</v>
+      </c>
+      <c r="C652" t="s">
+        <v>52</v>
+      </c>
+      <c r="D652" t="s">
+        <v>53</v>
+      </c>
+      <c r="E652" t="s">
+        <v>4156</v>
+      </c>
+      <c r="F652" t="s">
+        <v>4156</v>
+      </c>
+      <c r="G652" t="s">
+        <v>769</v>
+      </c>
+      <c r="H652" t="s">
+        <v>770</v>
+      </c>
+      <c r="I652" t="s">
+        <v>56</v>
+      </c>
+      <c r="K652" t="s">
+        <v>5517</v>
+      </c>
+      <c r="L652" t="s">
+        <v>5002</v>
+      </c>
+      <c r="M652">
+        <v>-14.944211299999999</v>
+      </c>
+      <c r="N652">
+        <v>38.321587800000003</v>
+      </c>
+      <c r="O652">
+        <v>98.400001525878906</v>
+      </c>
+      <c r="P652">
+        <v>516.89996337890625</v>
+      </c>
+      <c r="Q652" t="s">
+        <v>4239</v>
+      </c>
+      <c r="R652" t="s">
+        <v>56</v>
+      </c>
+      <c r="S652" t="s">
+        <v>59</v>
+      </c>
+      <c r="T652" t="s">
+        <v>5003</v>
+      </c>
+      <c r="U652" t="s">
+        <v>61</v>
+      </c>
+      <c r="V652">
+        <v>2003</v>
+      </c>
+      <c r="W652">
+        <v>23</v>
+      </c>
+      <c r="X652" t="s">
+        <v>448</v>
+      </c>
+      <c r="Y652" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z652" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA652" t="s">
+        <v>1280</v>
+      </c>
+      <c r="AB652" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC652" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD652" t="s">
+        <v>998</v>
+      </c>
+      <c r="AE652" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF652" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG652" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH652" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI652" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM652" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN652" t="s">
+        <v>67</v>
+      </c>
+      <c r="AO652" t="s">
+        <v>4406</v>
+      </c>
+      <c r="AP652" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ652" t="s">
+        <v>495</v>
+      </c>
+      <c r="AR652" t="s">
+        <v>5004</v>
+      </c>
+      <c r="AS652" t="s">
+        <v>1960</v>
+      </c>
+      <c r="AT652">
+        <v>0.96097294192806493</v>
+      </c>
+      <c r="AU652">
+        <v>0</v>
+      </c>
+      <c r="AV652" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW652">
+        <v>2105</v>
       </c>
     </row>
   </sheetData>
@@ -101553,15 +102369,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -101796,6 +102603,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3338ADEC-8CAE-41B2-8D8F-5460C83CEB8B}">
   <ds:schemaRefs>
@@ -101808,13 +102624,13 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{212EFCB9-6160-46C4-9327-D087D97EA86F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7FAAC4-DCCC-45D2-BE24-F32F04F78BEF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5FD3D55-B5F3-4187-969C-66F30B4F3ECB}"/>
 </file>
--- a/Selecionados_Motivacional_Ribaue_2026.xlsx
+++ b/Selecionados_Motivacional_Ribaue_2026.xlsx
@@ -102358,19 +102358,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
     <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
     <xsd:element name="properties">
@@ -102443,7 +102441,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -102466,7 +102464,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -102485,7 +102483,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -102513,8 +102511,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -102604,15 +102602,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7FAAC4-DCCC-45D2-BE24-F32F04F78BEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{675D1D34-F605-4D6E-97B6-E03752A395F3}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3338ADEC-8CAE-41B2-8D8F-5460C83CEB8B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -102621,16 +102633,4 @@
     <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{212EFCB9-6160-46C4-9327-D087D97EA86F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7FAAC4-DCCC-45D2-BE24-F32F04F78BEF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Selecionados_Motivacional_Ribaue_2026.xlsx
+++ b/Selecionados_Motivacional_Ribaue_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/Abrindo_Oportunidades/2026/Dash_Abrindo_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_F833A363A5E9B997DDF5DE690BDD84802C57B85D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC16045-D8FA-4B38-801B-465B84FE8500}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_F833A363A5E9B997DDF5DE690BDD84802C57B85D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA921BEB-7346-41C2-8B67-CC1234242C11}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22699" uniqueCount="5518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22732" uniqueCount="5527">
   <si>
     <t>interview__key</t>
   </si>
@@ -16574,6 +16574,33 @@
   </si>
   <si>
     <t>RICARDINA JULIO</t>
+  </si>
+  <si>
+    <t>81-08-89-43</t>
+  </si>
+  <si>
+    <t>10173fd0bc574b2eb97728d142bd8d56</t>
+  </si>
+  <si>
+    <t>ALFEU JULIO</t>
+  </si>
+  <si>
+    <t>2026-02-16T12:18:09</t>
+  </si>
+  <si>
+    <t>2026-02-16T10:18:10</t>
+  </si>
+  <si>
+    <t>032107742496N</t>
+  </si>
+  <si>
+    <t>MILHO CEBOLA FEIJAO HOLOCO BOER</t>
+  </si>
+  <si>
+    <t>872-695-240</t>
+  </si>
+  <si>
+    <t>855-618-992</t>
   </si>
 </sst>
 </file>
@@ -17005,7 +17032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX652"/>
+  <dimension ref="A1:AX653"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.21875" customWidth="1"/>
@@ -102349,6 +102376,134 @@
         <v>2105</v>
       </c>
     </row>
+    <row r="653" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A653" t="s">
+        <v>5518</v>
+      </c>
+      <c r="B653" t="s">
+        <v>5519</v>
+      </c>
+      <c r="C653" t="s">
+        <v>52</v>
+      </c>
+      <c r="D653" t="s">
+        <v>53</v>
+      </c>
+      <c r="E653" t="s">
+        <v>4156</v>
+      </c>
+      <c r="F653" t="s">
+        <v>4156</v>
+      </c>
+      <c r="G653" t="s">
+        <v>769</v>
+      </c>
+      <c r="I653" t="s">
+        <v>56</v>
+      </c>
+      <c r="K653" t="s">
+        <v>5520</v>
+      </c>
+      <c r="L653" t="s">
+        <v>5521</v>
+      </c>
+      <c r="M653">
+        <v>-14.9444696</v>
+      </c>
+      <c r="N653">
+        <v>38.322583299999998</v>
+      </c>
+      <c r="O653">
+        <v>100</v>
+      </c>
+      <c r="P653">
+        <v>516.5</v>
+      </c>
+      <c r="Q653" t="s">
+        <v>5522</v>
+      </c>
+      <c r="R653" t="s">
+        <v>56</v>
+      </c>
+      <c r="S653" t="s">
+        <v>244</v>
+      </c>
+      <c r="T653" t="s">
+        <v>5523</v>
+      </c>
+      <c r="U653" t="s">
+        <v>102</v>
+      </c>
+      <c r="V653">
+        <v>2004</v>
+      </c>
+      <c r="W653">
+        <v>2004</v>
+      </c>
+      <c r="X653" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y653" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z653" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA653" t="s">
+        <v>5524</v>
+      </c>
+      <c r="AB653" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC653" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE653" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF653" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG653" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH653" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI653" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ653" t="s">
+        <v>5525</v>
+      </c>
+      <c r="AK653" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM653" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN653" t="s">
+        <v>135</v>
+      </c>
+      <c r="AO653" t="s">
+        <v>5526</v>
+      </c>
+      <c r="AP653" t="s">
+        <v>56</v>
+      </c>
+      <c r="AT653">
+        <v>0.30096581731967897</v>
+      </c>
+      <c r="AU653">
+        <v>0</v>
+      </c>
+      <c r="AV653" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW653">
+        <v>2099</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -102358,15 +102513,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -102601,6 +102747,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -102613,15 +102768,30 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{675D1D34-F605-4D6E-97B6-E03752A395F3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7FAAC4-DCCC-45D2-BE24-F32F04F78BEF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{675D1D34-F605-4D6E-97B6-E03752A395F3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
